--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:42:43+00:00</t>
+    <t>2026-06-22T14:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,7 +475,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:38:01+00:00</t>
+    <t>2026-06-29T12:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:42:10+00:00</t>
+    <t>2026-07-07T09:34:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -911,7 +911,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260619134041</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T09:34:50+00:00</t>
+    <t>2026-07-16T11:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:52:18+00:00</t>
+    <t>2026-07-16T13:43:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:43:45+00:00</t>
+    <t>2026-07-16T16:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T16:12:39+00:00</t>
+    <t>2026-07-20T14:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:23:22+00:00</t>
+    <t>2026-08-12T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:16:17+00:00</t>
+    <t>2026-08-13T08:08:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:08:00+00:00</t>
+    <t>2026-08-13T08:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:33:40+00:00</t>
+    <t>2026-08-13T08:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T08:58:16+00:00</t>
+    <t>2026-08-13T09:15:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:15:12+00:00</t>
+    <t>2026-08-13T09:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:41:50+00:00</t>
+    <t>2026-08-13T12:00:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="569">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:00:16+00:00</t>
+    <t>2026-08-13T12:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -688,11 +688,11 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-medication-administration|2.2.0)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
-    <t>Posologie</t>
+    <t>Information that supports the dispensing of the medication</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -1683,14 +1683,6 @@
   </si>
   <si>
     <t>A code signifying whether a different drug was dispensed from what was prescribed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;code value="G"/&gt;
-    &lt;display value="Substitution autorisée par un produit générique"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>A coded concept describing whether a different medicinal product may be dispensed other than the product as specified exactly in the prescription.</t>
@@ -4261,7 +4253,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -5303,7 +5295,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>89</v>
@@ -10677,7 +10669,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>89</v>
@@ -10710,7 +10702,7 @@
         <v>79</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>539</v>
+        <v>79</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>79</v>
@@ -10728,10 +10720,10 @@
         <v>176</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>79</v>
@@ -10773,18 +10765,18 @@
         <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>543</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10810,10 +10802,10 @@
         <v>182</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10843,11 +10835,11 @@
         <v>176</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="Z75" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>548</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10864,7 +10856,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10882,13 +10874,13 @@
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -10896,10 +10888,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10922,13 +10914,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10979,7 +10971,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -10997,13 +10989,13 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11011,14 +11003,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11037,16 +11029,16 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11096,7 +11088,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11114,7 +11106,7 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
@@ -11128,10 +11120,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11154,16 +11146,16 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11213,7 +11205,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11231,7 +11223,7 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
